--- a/templates/monthly-report.xlsx
+++ b/templates/monthly-report.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="10月" sheetId="1" r:id="r1"/>
-    <sheet name="11月" sheetId="2" r:id="r2"/>
-    <sheet name="12月" sheetId="3" r:id="r3"/>
-    <sheet name="1月" sheetId="4" r:id="r4"/>
-    <sheet name="2月" sheetId="5" r:id="r5"/>
-    <sheet name="3月" sheetId="6" r:id="r6"/>
-    <sheet name="4月" sheetId="7" r:id="r7"/>
-    <sheet name="5月" sheetId="8" r:id="r8"/>
-    <sheet name="6月" sheetId="9" r:id="r9"/>
-    <sheet name="7月" sheetId="10" r:id="r10"/>
-    <sheet name="8月" sheetId="11" r:id="r11"/>
-    <sheet name="9月" sheetId="12" r:id="r12"/>
+    <sheet name="1月" sheetId="1" r:id="r1"/>
+    <sheet name="2月" sheetId="2" r:id="r2"/>
+    <sheet name="3月" sheetId="3" r:id="r3"/>
+    <sheet name="4月" sheetId="4" r:id="r4"/>
+    <sheet name="5月" sheetId="5" r:id="r5"/>
+    <sheet name="6月" sheetId="6" r:id="r6"/>
+    <sheet name="7月" sheetId="7" r:id="r7"/>
+    <sheet name="8月" sheetId="8" r:id="r8"/>
+    <sheet name="9月" sheetId="9" r:id="r9"/>
+    <sheet name="10月" sheetId="10" r:id="r10"/>
+    <sheet name="11月" sheetId="11" r:id="r11"/>
+    <sheet name="12月" sheetId="12" r:id="r12"/>
     <sheet name="年間まとめ" sheetId="13" r:id="r13"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -21,117 +21,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 1月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 基本数値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 新しく販売した作品数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">② 販売中の作品数（合計）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ SNSの投稿数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 販売先別の売上（その月に売れた分）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">販売先</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上（手数料を引く前）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手取り（手数料を引いた後）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">販売部数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売れた作品名・メモ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kindle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOOTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLsite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FANZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他（　　　　）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記入ガイド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　・黄色セル（青字）＝入力欄／緑セル（黒字）＝自動計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　・毎月初めに、先月売れた分を入力してください（入金された月ではなく、売れた月で記録）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　・売上＝手数料を引く前の金額、手取り＝手数料などを引いた後に受け取る金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　・数字だけを入力してください（「円」やカンマは不要です）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　・売れなかった販売先は空欄のままでOKです</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 2月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 3月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 4月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 5月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 6月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 7月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 8月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 9月</t>
+  </si>
   <si>
     <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 10月</t>
   </si>
   <si>
-    <t xml:space="preserve">■ 基本数値</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 新しく販売した作品数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">② 販売中の作品数（合計）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ SNSの投稿数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 販売先別の売上（その月に売れた分）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">販売先</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売上（手数料を引く前）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手取り（手数料を引いた後）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手数料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">販売部数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売れた作品名・メモ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kindle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOOTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLsite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FANZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その他（　　　　）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">記入ガイド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　・黄色セル（青字）＝入力欄／緑セル（黒字）＝自動計算</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　・毎月初めに、先月売れた分を入力してください（入金された月ではなく、売れた月で記録）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　・売上＝手数料を引く前の金額、手取り＝手数料などを引いた後に受け取る金額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　・数字だけを入力してください（「円」やカンマは不要です）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　・売れなかった販売先は空欄のままでOKです</t>
-  </si>
-  <si>
     <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 11月</t>
   </si>
   <si>
     <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2026年 12月</t>
   </si>
   <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 1月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 2月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 3月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 4月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 5月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 6月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 7月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 8月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次レポート｜お名前：＿＿＿＿＿＿＿＿｜2027年 9月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年間まとめ｜お名前：＿＿＿＿＿＿＿＿｜2026年10月〜2027年9月</t>
+    <t xml:space="preserve">年間まとめ｜お名前：＿＿＿＿＿＿＿＿｜2026年1月〜2026年12月</t>
   </si>
   <si>
     <t xml:space="preserve">各月のタブから自動で集計されます（入力不要）</t>
@@ -146,9 +143,6 @@
     <t xml:space="preserve">手取り合計</t>
   </si>
   <si>
-    <t xml:space="preserve">手数料合計</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kindle 手取り</t>
   </si>
   <si>
@@ -164,6 +158,33 @@
     <t xml:space="preserve">その他 手取り</t>
   </si>
   <si>
+    <t xml:space="preserve">2026年1月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年2月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年3月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年4月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年5月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年6月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年7月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年8月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年9月</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026年10月</t>
   </si>
   <si>
@@ -171,33 +192,6 @@
   </si>
   <si>
     <t xml:space="preserve">2026年12月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年1月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年2月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年3月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年4月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年5月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年6月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年7月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年8月</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027年9月</t>
   </si>
 </sst>
 </file>
@@ -364,11 +358,10 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -426,89 +419,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -516,49 +491,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -573,16 +545,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -635,89 +606,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -725,49 +678,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -782,16 +732,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -844,89 +793,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -934,49 +865,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -991,16 +919,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -1053,89 +980,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -1143,49 +1052,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1201,26 +1107,28 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2">
-      <c t="s">
+    <row r="4" ht="32" customHeight="1">
+      <c t="s" s="6">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
       <c t="s" s="6">
         <v>38</v>
       </c>
@@ -1228,15 +1136,15 @@
         <v>39</v>
       </c>
       <c t="s" s="6">
+        <v>10</v>
+      </c>
+      <c t="s" s="6">
         <v>40</v>
       </c>
       <c t="s" s="6">
         <v>41</v>
       </c>
       <c t="s" s="6">
-        <v>11</v>
-      </c>
-      <c t="s" s="6">
         <v>42</v>
       </c>
       <c t="s" s="6">
@@ -1245,93 +1153,339 @@
       <c t="s" s="6">
         <v>44</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c t="s" s="4">
         <v>45</v>
       </c>
-      <c t="s" s="6">
+      <c s="9">
+        <f>'1月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'1月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'1月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'1月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'1月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'1月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'1月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'1月'!D14</f>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c t="s" s="4">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
+      <c s="9">
+        <f>'2月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'2月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'2月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'2月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'2月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'2月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'2月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'2月'!D14</f>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c t="s" s="4">
         <v>47</v>
       </c>
       <c s="9">
+        <f>'3月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'3月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'3月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'3月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'3月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'3月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'3月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'3月'!D14</f>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>48</v>
+      </c>
+      <c s="9">
+        <f>'4月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'4月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'4月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'4月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'4月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'4月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'4月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'4月'!D14</f>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>49</v>
+      </c>
+      <c s="9">
+        <f>'5月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'5月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'5月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'5月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'5月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'5月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'5月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'5月'!D14</f>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>50</v>
+      </c>
+      <c s="9">
+        <f>'6月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'6月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'6月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'6月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'6月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'6月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'6月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'6月'!D14</f>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>51</v>
+      </c>
+      <c s="9">
+        <f>'7月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'7月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'7月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'7月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'7月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'7月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'7月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'7月'!D14</f>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>52</v>
+      </c>
+      <c s="9">
+        <f>'8月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'8月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'8月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'8月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'8月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'8月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'8月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'8月'!D14</f>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>53</v>
+      </c>
+      <c s="9">
+        <f>'9月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'9月'!D15</f>
+      </c>
+      <c s="14">
+        <f>'9月'!E15</f>
+      </c>
+      <c s="9">
+        <f>'9月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'9月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'9月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'9月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'9月'!D14</f>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>54</v>
+      </c>
+      <c s="9">
         <f>'10月'!C15</f>
       </c>
       <c s="9">
         <f>'10月'!D15</f>
       </c>
-      <c s="9">
+      <c s="14">
         <f>'10月'!E15</f>
       </c>
+      <c s="9">
+        <f>'10月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'10月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'10月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'10月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'10月'!D14</f>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>55</v>
+      </c>
+      <c s="9">
+        <f>'11月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'11月'!D15</f>
+      </c>
       <c s="14">
-        <f>'10月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'10月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'10月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'10月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'10月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'10月'!D14</f>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>48</v>
-      </c>
-      <c s="9">
-        <f>'11月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'11月'!D15</f>
-      </c>
-      <c s="9">
         <f>'11月'!E15</f>
       </c>
+      <c s="9">
+        <f>'11月'!D10</f>
+      </c>
+      <c s="9">
+        <f>'11月'!D11</f>
+      </c>
+      <c s="9">
+        <f>'11月'!D12</f>
+      </c>
+      <c s="9">
+        <f>'11月'!D13</f>
+      </c>
+      <c s="9">
+        <f>'11月'!D14</f>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c t="s" s="4">
+        <v>56</v>
+      </c>
+      <c s="9">
+        <f>'12月'!C15</f>
+      </c>
+      <c s="9">
+        <f>'12月'!D15</f>
+      </c>
       <c s="14">
-        <f>'11月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'11月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'11月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'11月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'11月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'11月'!D14</f>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>49</v>
-      </c>
-      <c s="9">
-        <f>'12月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'12月'!D15</f>
-      </c>
-      <c s="9">
         <f>'12月'!E15</f>
       </c>
-      <c s="14">
-        <f>'12月'!F15</f>
-      </c>
       <c s="9">
         <f>'12月'!D10</f>
       </c>
@@ -1348,297 +1502,9 @@
         <f>'12月'!D14</f>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>50</v>
-      </c>
-      <c s="9">
-        <f>'1月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'1月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'1月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'1月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'1月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'1月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'1月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'1月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'1月'!D14</f>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>51</v>
-      </c>
-      <c s="9">
-        <f>'2月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'2月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'2月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'2月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'2月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'2月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'2月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'2月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'2月'!D14</f>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>52</v>
-      </c>
-      <c s="9">
-        <f>'3月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'3月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'3月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'3月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'3月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'3月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'3月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'3月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'3月'!D14</f>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>53</v>
-      </c>
-      <c s="9">
-        <f>'4月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'4月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'4月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'4月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'4月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'4月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'4月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'4月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'4月'!D14</f>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>54</v>
-      </c>
-      <c s="9">
-        <f>'5月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'5月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'5月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'5月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'5月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'5月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'5月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'5月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'5月'!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>55</v>
-      </c>
-      <c s="9">
-        <f>'6月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'6月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'6月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'6月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'6月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'6月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'6月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'6月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'6月'!D14</f>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>56</v>
-      </c>
-      <c s="9">
-        <f>'7月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'7月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'7月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'7月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'7月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'7月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'7月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'7月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'7月'!D14</f>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>57</v>
-      </c>
-      <c s="9">
-        <f>'8月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'8月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'8月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'8月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'8月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'8月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'8月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'8月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'8月'!D14</f>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c t="s" s="4">
-        <v>58</v>
-      </c>
-      <c s="9">
-        <f>'9月'!C15</f>
-      </c>
-      <c s="9">
-        <f>'9月'!D15</f>
-      </c>
-      <c s="9">
-        <f>'9月'!E15</f>
-      </c>
-      <c s="14">
-        <f>'9月'!F15</f>
-      </c>
-      <c s="9">
-        <f>'9月'!D10</f>
-      </c>
-      <c s="9">
-        <f>'9月'!D11</f>
-      </c>
-      <c s="9">
-        <f>'9月'!D12</f>
-      </c>
-      <c s="9">
-        <f>'9月'!D13</f>
-      </c>
-      <c s="9">
-        <f>'9月'!D14</f>
-      </c>
-    </row>
     <row r="17" ht="20" customHeight="1">
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(B5:B16)</f>
@@ -1646,10 +1512,10 @@
       <c s="10">
         <f>SUM(C5:C16)</f>
       </c>
+      <c s="11">
+        <f>SUM(D5:D16)</f>
+      </c>
       <c s="10">
-        <f>SUM(D5:D16)</f>
-      </c>
-      <c s="11">
         <f>SUM(E5:E16)</f>
       </c>
       <c s="10">
@@ -1664,13 +1530,10 @@
       <c s="10">
         <f>SUM(I5:I16)</f>
       </c>
-      <c s="10">
-        <f>SUM(J5:J16)</f>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1685,16 +1548,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -1747,89 +1609,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -1837,49 +1681,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1894,16 +1735,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -1956,89 +1796,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -2046,49 +1868,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2103,16 +1922,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -2165,89 +1983,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -2255,49 +2055,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2312,16 +2109,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -2374,89 +2170,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -2464,49 +2242,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2521,16 +2296,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -2583,89 +2357,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -2673,49 +2429,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2730,16 +2483,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -2792,89 +2544,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -2882,49 +2616,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2939,16 +2670,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -3001,89 +2731,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -3091,49 +2803,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3148,16 +2857,15 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c t="s" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -3210,89 +2918,71 @@
       <c t="s" s="6">
         <v>11</v>
       </c>
-      <c t="s" s="6">
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c s="7">
+        <v>1</v>
+      </c>
+      <c t="s" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c s="7">
-        <v>1</v>
+      <c s="8"/>
+      <c s="8"/>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c s="7">
+        <v>2</v>
       </c>
       <c t="s" s="4">
         <v>13</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C10:D10)&lt;2,"",C10-D10)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c s="7">
-        <v>2</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c s="7">
+        <v>3</v>
       </c>
       <c t="s" s="4">
         <v>14</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C11:D11)&lt;2,"",C11-D11)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c s="7">
-        <v>3</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c s="7">
+        <v>4</v>
       </c>
       <c t="s" s="4">
         <v>15</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C12:D12)&lt;2,"",C12-D12)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c s="7">
-        <v>4</v>
+      <c s="5"/>
+      <c s="12"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c s="7">
+        <v>5</v>
       </c>
       <c t="s" s="4">
         <v>16</v>
       </c>
       <c s="8"/>
       <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C13:D13)&lt;2,"",C13-D13)</f>
-      </c>
-      <c s="5"/>
-      <c s="12"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c s="7">
-        <v>5</v>
-      </c>
-      <c t="s" s="4">
-        <v>17</v>
-      </c>
-      <c s="8"/>
-      <c s="8"/>
-      <c s="9">
-        <f>IF(COUNT(C14:D14)&lt;2,"",C14-D14)</f>
-      </c>
       <c s="5"/>
       <c s="12"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c s="4"/>
       <c t="s" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c s="10">
         <f>SUM(C10:C14)</f>
@@ -3300,49 +2990,46 @@
       <c s="10">
         <f>SUM(D10:D14)</f>
       </c>
-      <c s="10">
+      <c s="11">
         <f>SUM(E10:E14)</f>
-      </c>
-      <c s="11">
-        <f>SUM(F10:F14)</f>
       </c>
       <c s="4"/>
     </row>
     <row r="17">
       <c t="s" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="19">
       <c t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="20">
       <c t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="21">
       <c t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="22">
       <c t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
